--- a/Outputs/PtX_demand_LV.xlsx
+++ b/Outputs/PtX_demand_LV.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K37"/>
+  <dimension ref="A1:K43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,32 +488,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Hydrogen</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>2030</v>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="n">
-        <v>0.0001099455615804299</v>
-      </c>
+      <c r="C2" t="n">
+        <v>3.180807881356633e-05</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.0002119721346285768</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.0002947738125624284</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="n">
-        <v>2.994060962636904e-10</v>
-      </c>
-      <c r="I2" t="n">
-        <v>3.860388707617408e-05</v>
-      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>Hydrogen</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -522,17 +522,23 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" t="n">
+        <v>0.0001099455615804299</v>
+      </c>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+      <c r="H3" t="n">
+        <v>2.994060962636904e-10</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.860388707617408e-05</v>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ammonia</t>
+          <t>Methanol</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -551,7 +557,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Synthetic Gases</t>
+          <t>Ammonia</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -570,7 +576,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Biogenic Gases</t>
+          <t>Synthetic Gases</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -578,24 +584,18 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="n">
-        <v>0.0001292690832450209</v>
-      </c>
-      <c r="F6" t="n">
-        <v>3.30567711245205e-05</v>
-      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="n">
-        <v>8.433250237987777e-06</v>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Fossil Gases</t>
+          <t>Biogenic Gases</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -603,14 +603,16 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>0.0001292690832450209</v>
+      </c>
       <c r="F7" t="n">
-        <v>0.0004233207034683043</v>
+        <v>3.30567711245205e-05</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>3.103243109170354e-05</v>
+        <v>8.433250237987777e-06</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -618,7 +620,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Synthetic Liquids</t>
+          <t>Fossil Gases</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -627,17 +629,21 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+      <c r="F8" t="n">
+        <v>0.0004233207034683043</v>
+      </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="n">
+        <v>3.103243109170354e-05</v>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Biogenic Liquids</t>
+          <t>Synthetic Liquids</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -646,29 +652,17 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="n">
-        <v>0.001981514806922922</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1.153603373007916e-05</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.0008192039737558</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.001448152232451</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.0001641363495125</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.003883289897164569</v>
-      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Fossil Liquids</t>
+          <t>Biogenic Liquids</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -678,28 +672,28 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>0.0195930929982781</v>
+        <v>0.001981514806922922</v>
       </c>
       <c r="G10" t="n">
-        <v>8.12449026753831e-05</v>
+        <v>1.153603373007916e-05</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0074870826105117</v>
+        <v>0.0008192039737558</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0092620082230199</v>
+        <v>0.001448152232451</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0009935176689125</v>
+        <v>0.0001641363495125</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0380367361995503</v>
+        <v>0.003883289897164569</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Fossil Liquids</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -707,20 +701,30 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="n">
-        <v>0.003350289854749351</v>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="n">
+        <v>0.0195930929982781</v>
+      </c>
+      <c r="G11" t="n">
+        <v>8.12449026753831e-05</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.0074870826105117</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.0092620082230199</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.0009935176689125</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.0380367361995503</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Renewable Energy Carrier</t>
+          <t>Biomass [Solid]</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -729,7 +733,7 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
-        <v>0.0001247370465212553</v>
+        <v>0.003350289854749351</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
@@ -741,7 +745,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Overall Demand</t>
+          <t>Fossil Rest</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -750,83 +754,91 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>0.003604295984515627</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.02214093084137428</v>
-      </c>
-      <c r="G13" t="n">
-        <v>9.278093640546226e-05</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.008306286883673596</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.01078823002387677</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.001157654018425</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0.04192002609671487</v>
-      </c>
+        <v>0.002286055167896486</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Hydrogen</t>
+          <t>Renewable Energy Carrier</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2040</v>
+        <v>2030</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="n">
-        <v>0.000528630158911389</v>
-      </c>
+      <c r="E14" t="n">
+        <v>0.0001247370465212553</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" t="n">
-        <v>2.506359722087326e-08</v>
-      </c>
-      <c r="I14" t="n">
-        <v>5.850542560662657e-05</v>
-      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>Overall Demand</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2040</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+        <v>2030</v>
+      </c>
+      <c r="C15" t="n">
+        <v>3.180807881356633e-05</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.0002119721346285768</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.006185124964974541</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.02214093084137428</v>
+      </c>
+      <c r="G15" t="n">
+        <v>9.278093640546226e-05</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.008306286883673596</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.01078823002387677</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.001157654018425</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.04192002609671487</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ammonia</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>2040</v>
       </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
+      <c r="C16" t="n">
+        <v>4.253100103034853e-05</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.0002128062285760544</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.0002912593560803535</v>
+      </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
@@ -837,7 +849,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Synthetic Gases</t>
+          <t>Hydrogen</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -847,12 +859,14 @@
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
-        <v>1.929666961373647e-10</v>
+        <v>0.000528630158911389</v>
       </c>
       <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="H17" t="n">
+        <v>2.506359722087326e-08</v>
+      </c>
       <c r="I17" t="n">
-        <v>1.916114023620643e-11</v>
+        <v>5.850542560662657e-05</v>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
@@ -860,7 +874,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Biogenic Gases</t>
+          <t>Methanol</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -868,24 +882,18 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
-      <c r="E18" t="n">
-        <v>0.0005213250276825129</v>
-      </c>
-      <c r="F18" t="n">
-        <v>4.082073675471693e-05</v>
-      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
-      <c r="I18" t="n">
-        <v>1.321156621240186e-05</v>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Fossil Gases</t>
+          <t>Ammonia</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -894,21 +902,17 @@
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
-      <c r="F19" t="n">
-        <v>0.0002288789322165449</v>
-      </c>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" t="n">
-        <v>3.324458242322907e-05</v>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Synthetic Liquids</t>
+          <t>Synthetic Gases</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -917,17 +921,21 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
+      <c r="F20" t="n">
+        <v>1.929666961373647e-10</v>
+      </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="n">
+        <v>1.916114023620643e-11</v>
+      </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Biogenic Liquids</t>
+          <t>Biogenic Gases</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -935,30 +943,24 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
+      <c r="E21" t="n">
+        <v>0.0005213250276825129</v>
+      </c>
       <c r="F21" t="n">
-        <v>0.0008541260658841722</v>
-      </c>
-      <c r="G21" t="n">
-        <v>1.880563813522519e-05</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.0009972637664711001</v>
-      </c>
+        <v>4.082073675471693e-05</v>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
-        <v>0.0009728642046391999</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.0001993990255969</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0.004393672108948045</v>
-      </c>
+        <v>1.321156621240186e-05</v>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Fossil Liquids</t>
+          <t>Fossil Gases</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -968,28 +970,20 @@
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="n">
-        <v>0.005287681407832443</v>
-      </c>
-      <c r="G22" t="n">
-        <v>8.734278736125689e-05</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.0070589198916128</v>
-      </c>
+        <v>0.0002288789322165449</v>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
-        <v>0.0042151413393947</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.0008816580460487</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0.03690103808435079</v>
-      </c>
+        <v>3.324458242322907e-05</v>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Synthetic Liquids</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -997,9 +991,7 @@
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="n">
-        <v>0.00327444339643678</v>
-      </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
@@ -1010,7 +1002,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Renewable Energy Carrier</t>
+          <t>Biogenic Liquids</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1018,20 +1010,30 @@
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" t="n">
-        <v>0.0005037909786558641</v>
-      </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="n">
+        <v>0.0008541260658841722</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1.880563813522519e-05</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.0009972637664711001</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.0009728642046391999</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.0001993990255969</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.004393672108948045</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Overall Demand</t>
+          <t>Fossil Liquids</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1039,65 +1041,61 @@
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" t="n">
-        <v>0.004299559402775157</v>
-      </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="n">
-        <v>0.006940137494565962</v>
+        <v>0.005287681407832443</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0001061484254964821</v>
+        <v>8.734278736125689e-05</v>
       </c>
       <c r="H25" t="n">
-        <v>0.008056208721681122</v>
+        <v>0.0070589198916128</v>
       </c>
       <c r="I25" t="n">
-        <v>0.005292967137437298</v>
+        <v>0.0042151413393947</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0010810570716456</v>
+        <v>0.0008816580460487</v>
       </c>
       <c r="K25" t="n">
-        <v>0.04129471019329883</v>
+        <v>0.03690103808435079</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Hydrogen</t>
+          <t>Biomass [Solid]</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2050</v>
+        <v>2040</v>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="n">
-        <v>0.0007330959630713696</v>
-      </c>
+      <c r="E26" t="n">
+        <v>0.00327444339643678</v>
+      </c>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
-      <c r="H26" t="n">
-        <v>4.248077845686649e-08</v>
-      </c>
-      <c r="I26" t="n">
-        <v>9.381509916396965e-05</v>
-      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>Fossil Rest</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2050</v>
+        <v>2040</v>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" t="n">
+        <v>0.001537674009507565</v>
+      </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
@@ -1108,15 +1106,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Ammonia</t>
+          <t>Renewable Energy Carrier</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2050</v>
+        <v>2040</v>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
+      <c r="E28" t="n">
+        <v>0.0005037909786558641</v>
+      </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
@@ -1127,55 +1127,69 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Synthetic Gases</t>
+          <t>Overall Demand</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2050</v>
-      </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
+        <v>2040</v>
+      </c>
+      <c r="C29" t="n">
+        <v>4.253100103034853e-05</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.0002128062285760544</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.006128492768363076</v>
+      </c>
       <c r="F29" t="n">
-        <v>1.753570821272777e-09</v>
-      </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+        <v>0.006940137494565962</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.0001061484254964821</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.008056208721681122</v>
+      </c>
       <c r="I29" t="n">
-        <v>5.667431723359336e-10</v>
-      </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+        <v>0.005292967137437298</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.0010810570716456</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.04129471019329883</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Biogenic Gases</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>2050</v>
       </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
+      <c r="C30" t="n">
+        <v>2.669631077890598e-05</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.0002115745102970352</v>
+      </c>
       <c r="E30" t="n">
-        <v>0.001287472808588804</v>
-      </c>
-      <c r="F30" t="n">
-        <v>6.922281595571464e-06</v>
-      </c>
+        <v>0.0002964492034625095</v>
+      </c>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
-      <c r="I30" t="n">
-        <v>3.700371475782918e-06</v>
-      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Fossil Gases</t>
+          <t>Hydrogen</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1185,12 +1199,14 @@
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="n">
-        <v>1.400966101383919e-05</v>
+        <v>0.0007330959630713696</v>
       </c>
       <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+      <c r="H31" t="n">
+        <v>4.248077845686649e-08</v>
+      </c>
       <c r="I31" t="n">
-        <v>1.191674399740055e-05</v>
+        <v>9.381509916396965e-05</v>
       </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
@@ -1198,7 +1214,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Synthetic Liquids</t>
+          <t>Methanol</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -1207,29 +1223,17 @@
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
-      <c r="F32" t="n">
-        <v>3.792808597832266e-12</v>
-      </c>
-      <c r="G32" t="n">
-        <v>6.925100088031969e-13</v>
-      </c>
-      <c r="H32" t="n">
-        <v>3.842186310949697e-11</v>
-      </c>
-      <c r="I32" t="n">
-        <v>1.559076016035077e-11</v>
-      </c>
-      <c r="J32" t="n">
-        <v>1.36564917206143e-12</v>
-      </c>
-      <c r="K32" t="n">
-        <v>3.006501821266712e-10</v>
-      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Biogenic Liquids</t>
+          <t>Ammonia</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1238,29 +1242,17 @@
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="n">
-        <v>7.815856191631849e-05</v>
-      </c>
-      <c r="G33" t="n">
-        <v>3.360237361493725e-05</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0.0013062006708534</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0.0002521398314408</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0.0002564587227705</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0.006259399143320436</v>
-      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Fossil Liquids</t>
+          <t>Synthetic Gases</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -1270,28 +1262,20 @@
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="n">
-        <v>0.0002536165562991086</v>
-      </c>
-      <c r="G34" t="n">
-        <v>7.877949520192128e-05</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0.0064015315948016</v>
-      </c>
+        <v>1.753570821272777e-09</v>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
-        <v>0.0007427358011125</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0.0007588879544748</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0.03440180948670571</v>
-      </c>
+        <v>5.667431723359336e-10</v>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Biogenic Gases</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1300,19 +1284,23 @@
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="n">
-        <v>0.003386748319410228</v>
-      </c>
-      <c r="F35" t="inlineStr"/>
+        <v>0.001287472808588804</v>
+      </c>
+      <c r="F35" t="n">
+        <v>6.922281595571464e-06</v>
+      </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="n">
+        <v>3.700371475782918e-06</v>
+      </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Renewable Energy Carrier</t>
+          <t>Fossil Gases</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -1320,20 +1308,22 @@
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" t="n">
-        <v>0.001241439407242074</v>
-      </c>
-      <c r="F36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="n">
+        <v>1.400966101383919e-05</v>
+      </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
+      <c r="I36" t="n">
+        <v>1.191674399740055e-05</v>
+      </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Overall Demand</t>
+          <t>Synthetic Liquids</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1341,25 +1331,183 @@
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" t="n">
-        <v>0.005915660535241106</v>
-      </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="n">
+        <v>3.792808597832266e-12</v>
+      </c>
+      <c r="G37" t="n">
+        <v>6.925100088031969e-13</v>
+      </c>
+      <c r="H37" t="n">
+        <v>3.842186310949697e-11</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1.559076016035077e-11</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.36564917206143e-12</v>
+      </c>
+      <c r="K37" t="n">
+        <v>3.006501821266712e-10</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Biogenic Liquids</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="n">
+        <v>7.815856191631849e-05</v>
+      </c>
+      <c r="G38" t="n">
+        <v>3.360237361493725e-05</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.0013062006708534</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.0002521398314408</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.0002564587227705</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0.006259399143320436</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Fossil Liquids</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="n">
+        <v>0.0002536165562991086</v>
+      </c>
+      <c r="G39" t="n">
+        <v>7.877949520192128e-05</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.0064015315948016</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.0007427358011125</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.0007588879544748</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.03440180948670571</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Biomass [Solid]</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="n">
+        <v>0.003386748319410228</v>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Fossil Rest</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Renewable Energy Carrier</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="n">
+        <v>0.001241439407242074</v>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Overall Demand</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C43" t="n">
+        <v>2.669631077890598e-05</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.0002115745102970352</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.006212109738703616</v>
+      </c>
+      <c r="F43" t="n">
         <v>0.001085804781259837</v>
       </c>
-      <c r="G37" t="n">
+      <c r="G43" t="n">
         <v>0.0001123818695093686</v>
       </c>
-      <c r="H37" t="n">
+      <c r="H43" t="n">
         <v>0.00770777478485532</v>
       </c>
-      <c r="I37" t="n">
+      <c r="I43" t="n">
         <v>0.001104308429524385</v>
       </c>
-      <c r="J37" t="n">
+      <c r="J43" t="n">
         <v>0.001015346678610949</v>
       </c>
-      <c r="K37" t="n">
+      <c r="K43" t="n">
         <v>0.04066120893067633</v>
       </c>
     </row>

--- a/Outputs/PtX_demand_LV.xlsx
+++ b/Outputs/PtX_demand_LV.xlsx
@@ -503,11 +503,19 @@
       <c r="E2" t="n">
         <v>0.0002947738125624284</v>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
+      <c r="F2" t="n">
+        <v>0.002408716174825778</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.0004671275484928</v>
+      </c>
       <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="I2" t="n">
+        <v>0.0006282312247357</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.0014874277498943</v>
+      </c>
       <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
@@ -724,7 +732,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Fossil Residuals</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -733,7 +741,7 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
-        <v>0.003350289854749351</v>
+        <v>0.002286055167896486</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
@@ -745,7 +753,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Fossil Rest</t>
+          <t>Biomass [Solid]</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -754,7 +762,7 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>0.002286055167896486</v>
+        <v>0.003350289854749351</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
@@ -803,19 +811,19 @@
         <v>0.006185124964974541</v>
       </c>
       <c r="F15" t="n">
-        <v>0.02214093084137428</v>
+        <v>0.02454964701620006</v>
       </c>
       <c r="G15" t="n">
-        <v>9.278093640546226e-05</v>
+        <v>0.0005599084848982623</v>
       </c>
       <c r="H15" t="n">
         <v>0.008306286883673596</v>
       </c>
       <c r="I15" t="n">
-        <v>0.01078823002387677</v>
+        <v>0.01141646124861247</v>
       </c>
       <c r="J15" t="n">
-        <v>0.001157654018425</v>
+        <v>0.0026450817683193</v>
       </c>
       <c r="K15" t="n">
         <v>0.04192002609671487</v>
@@ -839,11 +847,19 @@
       <c r="E16" t="n">
         <v>0.0002912593560803535</v>
       </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
+      <c r="F16" t="n">
+        <v>0.006849303336398848</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.0005482172644094</v>
+      </c>
       <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+      <c r="I16" t="n">
+        <v>0.0022724746679859</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.0014669494208874</v>
+      </c>
       <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
@@ -1064,7 +1080,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Fossil Residuals</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1073,7 +1089,7 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="n">
-        <v>0.00327444339643678</v>
+        <v>0.001537674009507565</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
@@ -1085,7 +1101,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Fossil Rest</t>
+          <t>Biomass [Solid]</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1094,7 +1110,7 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="n">
-        <v>0.001537674009507565</v>
+        <v>0.00327444339643678</v>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
@@ -1143,19 +1159,19 @@
         <v>0.006128492768363076</v>
       </c>
       <c r="F29" t="n">
-        <v>0.006940137494565962</v>
+        <v>0.01378944083096481</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0001061484254964821</v>
+        <v>0.0006543656899058821</v>
       </c>
       <c r="H29" t="n">
         <v>0.008056208721681122</v>
       </c>
       <c r="I29" t="n">
-        <v>0.005292967137437298</v>
+        <v>0.007565441805423198</v>
       </c>
       <c r="J29" t="n">
-        <v>0.0010810570716456</v>
+        <v>0.002548006492533</v>
       </c>
       <c r="K29" t="n">
         <v>0.04129471019329883</v>
@@ -1179,11 +1195,19 @@
       <c r="E30" t="n">
         <v>0.0002964492034625095</v>
       </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
+      <c r="F30" t="n">
+        <v>0.007978806780585332</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.0006156447838719001</v>
+      </c>
       <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+      <c r="I30" t="n">
+        <v>0.0034583926904909</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.0014982307393895</v>
+      </c>
       <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
@@ -1416,7 +1440,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Fossil Residuals</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -1424,9 +1448,7 @@
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" t="n">
-        <v>0.003386748319410228</v>
-      </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
@@ -1437,7 +1459,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Fossil Rest</t>
+          <t>Biomass [Solid]</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -1445,7 +1467,9 @@
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
+      <c r="E41" t="n">
+        <v>0.003386748319410228</v>
+      </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
@@ -1493,19 +1517,19 @@
         <v>0.006212109738703616</v>
       </c>
       <c r="F43" t="n">
-        <v>0.001085804781259837</v>
+        <v>0.00906461156184517</v>
       </c>
       <c r="G43" t="n">
-        <v>0.0001123818695093686</v>
+        <v>0.0007280266533812686</v>
       </c>
       <c r="H43" t="n">
         <v>0.00770777478485532</v>
       </c>
       <c r="I43" t="n">
-        <v>0.001104308429524385</v>
+        <v>0.004562701120015286</v>
       </c>
       <c r="J43" t="n">
-        <v>0.001015346678610949</v>
+        <v>0.002513577418000449</v>
       </c>
       <c r="K43" t="n">
         <v>0.04066120893067633</v>
